--- a/Codes/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
+++ b/Codes/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
@@ -470,13 +470,13 @@
         <v>2024</v>
       </c>
       <c r="C2" t="n">
-        <v>18.57999999999999</v>
+        <v>5.700000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>17.02958106994629</v>
+        <v>2.681331634521484</v>
       </c>
       <c r="E2" t="n">
-        <v>1.550418930053706</v>
+        <v>3.018668365478517</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>29.38</v>
+        <v>52.72000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>16.17756080627441</v>
+        <v>2.668197870254517</v>
       </c>
       <c r="E3" t="n">
-        <v>13.20243919372558</v>
+        <v>50.0518021297455</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>5.700000000000001</v>
+        <v>30.53</v>
       </c>
       <c r="D4" t="n">
-        <v>15.45103740692139</v>
+        <v>2.739957809448242</v>
       </c>
       <c r="E4" t="n">
-        <v>9.751037406921386</v>
+        <v>27.79004219055176</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>52.72000000000001</v>
+        <v>17.92</v>
       </c>
       <c r="D5" t="n">
-        <v>14.95574569702148</v>
+        <v>3.260250091552734</v>
       </c>
       <c r="E5" t="n">
-        <v>37.76425430297853</v>
+        <v>14.65974990844726</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2024</v>
       </c>
       <c r="C6" t="n">
-        <v>30.53</v>
+        <v>14.47</v>
       </c>
       <c r="D6" t="n">
-        <v>17.01813125610352</v>
+        <v>2.562058687210083</v>
       </c>
       <c r="E6" t="n">
-        <v>13.51186874389649</v>
+        <v>11.90794131278992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2024</v>
       </c>
       <c r="C7" t="n">
-        <v>17.92</v>
+        <v>8.039999999999997</v>
       </c>
       <c r="D7" t="n">
-        <v>14.10332679748535</v>
+        <v>2.447806835174561</v>
       </c>
       <c r="E7" t="n">
-        <v>3.816673202514647</v>
+        <v>5.592193164825437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2024</v>
       </c>
       <c r="C8" t="n">
-        <v>14.47</v>
+        <v>5.25</v>
       </c>
       <c r="D8" t="n">
-        <v>13.44704532623291</v>
+        <v>2.515963792800903</v>
       </c>
       <c r="E8" t="n">
-        <v>1.02295467376709</v>
+        <v>2.734036207199097</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2024</v>
       </c>
       <c r="C9" t="n">
-        <v>8.039999999999997</v>
+        <v>35.45</v>
       </c>
       <c r="D9" t="n">
-        <v>13.4316520690918</v>
+        <v>2.829774856567383</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3916520690918</v>
+        <v>32.62022514343262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2024</v>
       </c>
       <c r="C10" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>15.23293304443359</v>
+        <v>2.602046966552734</v>
       </c>
       <c r="E10" t="n">
-        <v>9.982933044433594</v>
+        <v>1.397953033447266</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2024</v>
       </c>
       <c r="C11" t="n">
-        <v>35.45</v>
+        <v>21.05999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>15.2843189239502</v>
+        <v>2.645627498626709</v>
       </c>
       <c r="E11" t="n">
-        <v>20.16568107604981</v>
+        <v>18.41437250137328</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2024</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>7.490000000000002</v>
       </c>
       <c r="D12" t="n">
-        <v>15.46640300750732</v>
+        <v>3.276733636856079</v>
       </c>
       <c r="E12" t="n">
-        <v>11.46640300750732</v>
+        <v>4.213266363143923</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.05999999999999</v>
+        <v>6.789999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>18.74823188781738</v>
+        <v>2.832376003265381</v>
       </c>
       <c r="E13" t="n">
-        <v>2.311768112182609</v>
+        <v>3.957623996734618</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2024</v>
       </c>
       <c r="C14" t="n">
-        <v>7.490000000000002</v>
+        <v>35.99000000000002</v>
       </c>
       <c r="D14" t="n">
-        <v>18.71344375610352</v>
+        <v>2.450252294540405</v>
       </c>
       <c r="E14" t="n">
-        <v>11.22344375610351</v>
+        <v>33.53974770545961</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         <v>2024</v>
       </c>
       <c r="C15" t="n">
-        <v>6.789999999999999</v>
+        <v>8.919999999999998</v>
       </c>
       <c r="D15" t="n">
-        <v>16.82040405273438</v>
+        <v>2.754246711730957</v>
       </c>
       <c r="E15" t="n">
-        <v>10.03040405273438</v>
+        <v>6.165753288269041</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>35.99000000000002</v>
+        <v>6.200000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>13.75077438354492</v>
+        <v>2.951012372970581</v>
       </c>
       <c r="E16" t="n">
-        <v>22.23922561645509</v>
+        <v>3.24898762702942</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
